--- a/survey_templates/039_social_care_digital_transformation_survey--survey_templates.xlsx
+++ b/survey_templates/039_social_care_digital_transformation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>intro_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>page 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the Social Care Digital Transformation Survey!</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_1_question_1</t>
+          <t>tool_transform</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What digital transformation do you need help with?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Digital Transformation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What area of digital transformation would you like to help with?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_1_question_1_answer</t>
+          <t>tool_transform_answer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Please describe your chosen transformation</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provide more details about your chosen area</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>skill_development</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>page 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Skills Development</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What level of skills development do you need?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_2_question_1</t>
+          <t>skill_development_answer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How often will you use this new skill?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Please provide more details about your chosen skills development</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe how you will use these skills to achieve your goals</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_2_question_1_answer</t>
+          <t>frequency_use</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Frequency of Use</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How often would you use the new skill?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>page 3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Do you have any other feedback on our digital tools?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_3_question_1</t>
+          <t>feedback_answer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How do you rate your satisfaction with the digital tools you use?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Please provide your feedback</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Share your thoughts on how we can improve our digital tools</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,384 +736,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_3_question_1_answer</t>
+          <t>thanks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Thank you!</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thank you for taking the time to provide us feedback</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>page_4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>page 4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>page_4_question_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>What is your biggest challenge with digital tools?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>page_4_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>page 5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_5_question_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What is the most important skill you need help with?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_5_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_6</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>page 6</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_6_question_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How can we improve our digital tools?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_6_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>page 7</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_7_question_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Any other feedback?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_7_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_8</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page 8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_8_question_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thank you for taking the time to provide us feedback</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_8_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_9</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>page 9</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +770,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_1_question_1_choices</t>
+          <t>tool_transform_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +804,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Digital tools</t>
+          <t>Digital Tools</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_1_question_1_choices</t>
+          <t>tool_transform_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,14 +821,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Skills development</t>
+          <t>Skills Development</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_1_question_1_choices</t>
+          <t>tool_transform_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,102 +845,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_2_question_1_choices</t>
+          <t>skill_development_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>basic_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Basic Skills</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_2_question_1_choices</t>
+          <t>skill_development_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>intermediate_skills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Intermediate Skills</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_2_question_1_choices</t>
+          <t>skill_development_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>advanced_skills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Advanced Skills</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_5_question_1_choices</t>
+          <t>frequency_use_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>digital_tools</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Digital tools</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_5_question_1_choices</t>
+          <t>frequency_use_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>skills_development</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Skills development</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_5_question_1_choices</t>
+          <t>frequency_use_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>priorities</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Priorities</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
